--- a/artfynd/A 4180-2026 artfynd.xlsx
+++ b/artfynd/A 4180-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>91436325</v>
+        <v>120970134</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,47 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ösänget, Sjonkshävsmuren, Gstr</t>
+          <t>N om Ockelbo, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>590557</v>
+        <v>590158</v>
       </c>
       <c r="R2" t="n">
-        <v>6759216</v>
+        <v>6760091</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,12 +750,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2003-08-29</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2003-08-29</t>
+          <t>2024-04-23</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>08:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -757,28 +777,125 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Myr, kärr, i sumpskogskant mot öppen myr</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>Gst Fyndnr 264669N</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Marta Lomas Vega</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Marta Lomas Vega, Sanna Pousar</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>91436325</v>
+      </c>
+      <c r="B3" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ösänget, Sjonkshävsmuren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>590557</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6759216</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ockelbo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2003-08-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2003-08-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Myr, kärr, i sumpskogskant mot öppen myr</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>Gst Fyndnr 264669N</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Peter Ståhl</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Peter Ståhl</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Gästriklands flora (2016)</t>
         </is>
